--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1635,6 +1635,914 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sameer</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>09:26:40</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>21CS101</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sameer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>09:27:31</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>21CS101</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sameer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>09:28:02</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>21CS101</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sameer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>09:39:52</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>21CS101</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>sameer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>09:41:59</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>21CS101</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>sameer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>09:44:34</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>21CS101</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>sameer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>09:46:54</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>21CS101</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>sameer</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>09:48:26</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>21CS101</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>sameer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>09:49:39</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>21CS101</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Sameer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>15:53:10</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Sameer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>15:57:20</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>16:04:59</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>16:06:23</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>16:11:40</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>16:19:14</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>16:28:11</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>16:39:07</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>16:41:44</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>r</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>16:54:35</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>16:58:59</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>17:04:26</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>17:07:51</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>17:57:24</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>18:02:38</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>18:03:40</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>18:04:31</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>deepak</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>18:07:54</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>deepak</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>18:08:28</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>18:09:23</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>18:20:53</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>18:21:59</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>18:23:32</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>18:26:13</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>18:29:05</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>18:35:06</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>18:51:49</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>18:52:54</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>20:27:03</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>20:30:23</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>20:54:44</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>20:56:30</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>20:59:52</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Sameer.jpg</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>21:14:01</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>sameer deshpande</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>21:17:16</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
